--- a/libs/worker/src/test/fixtures/productos.xlsx
+++ b/libs/worker/src/test/fixtures/productos.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">CT-01005423</t>
   </si>
   <si>
-    <t xml:space="preserve">BANDEJA DISEÑO ELY GRANDE</t>
+    <t xml:space="preserve">Bandeja Diseño Ely Grande</t>
   </si>
   <si>
     <t xml:space="preserve">ELY</t>
@@ -92,7 +92,7 @@
     <t xml:space="preserve">CT-01002248</t>
   </si>
   <si>
-    <t xml:space="preserve">BANDEJA DISEÑO ELY MEDIANA</t>
+    <t xml:space="preserve">Bandeja Diseño Ely Mediana</t>
   </si>
   <si>
     <t xml:space="preserve">BANDEJA DISEÑO N8</t>
@@ -104,7 +104,7 @@
     <t xml:space="preserve">CT-01005430</t>
   </si>
   <si>
-    <t xml:space="preserve">BANDEJA DISEÑO ELY CHICA</t>
+    <t xml:space="preserve">Bandeja Diseño Ely Chica</t>
   </si>
   <si>
     <t xml:space="preserve">BANDEJA DISEÑO N6</t>
@@ -113,7 +113,7 @@
     <t xml:space="preserve">ELY-20025</t>
   </si>
   <si>
-    <t xml:space="preserve">TARJETA INVITACION ELY GLOBOS 6UN</t>
+    <t xml:space="preserve">Tarjeta Invitacion Ely Globos 6un</t>
   </si>
   <si>
     <t xml:space="preserve">MICRO J</t>
@@ -131,7 +131,7 @@
     <t xml:space="preserve">CP-ELY20005</t>
   </si>
   <si>
-    <t xml:space="preserve">BOLSAS SORPRESA ELY GLOBOS DISPLAY 6UN</t>
+    <t xml:space="preserve">Bolsas Sorpresa Ely Globos Display 6un</t>
   </si>
   <si>
     <t xml:space="preserve">BOLSA DULCES GLOBOS PEBD</t>
@@ -146,7 +146,7 @@
     <t xml:space="preserve">17805475004214</t>
   </si>
   <si>
-    <t xml:space="preserve">BOLSA P/DULCES INFANTIL ELY 10UN</t>
+    <t xml:space="preserve">Bolsa P/Dulces Infantil Ely 10un</t>
   </si>
   <si>
     <t xml:space="preserve">ORIGEN</t>
@@ -161,7 +161,7 @@
     <t xml:space="preserve">17805475005532</t>
   </si>
   <si>
-    <t xml:space="preserve">BOMBILLA ECO 20UN</t>
+    <t xml:space="preserve">Bombilla Eco 20un</t>
   </si>
   <si>
     <t xml:space="preserve">BIOELY</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">17805475007185</t>
   </si>
   <si>
-    <t xml:space="preserve">BOMBILLA PLA FLEXIBLE BIOELY 20 UN</t>
+    <t xml:space="preserve">Bombilla Pla Flexible Bioely 20 Un</t>
   </si>
   <si>
     <t xml:space="preserve">BOMBILLA FLEXIBLE </t>
@@ -191,7 +191,7 @@
     <t xml:space="preserve">DR-ELY-BROJA1+ZIZGAG</t>
   </si>
   <si>
-    <t xml:space="preserve">BOMBILLA PAPEL ELY 20 UND</t>
+    <t xml:space="preserve">Bombilla Papel Ely 20 Und</t>
   </si>
   <si>
     <t xml:space="preserve">DR-ELY-BROJA2+PUNT</t>
@@ -200,13 +200,13 @@
     <t xml:space="preserve">17898509282559</t>
   </si>
   <si>
-    <t xml:space="preserve">BOMBILLA PAPEL ELY 50 UND</t>
+    <t xml:space="preserve">Bombilla Papel Ely 50 Und</t>
   </si>
   <si>
     <t xml:space="preserve">ELY-20013</t>
   </si>
   <si>
-    <t xml:space="preserve">PIÑATA ELY</t>
+    <t xml:space="preserve">Piñata Ely</t>
   </si>
   <si>
     <t xml:space="preserve">PIÑATAS </t>
@@ -215,7 +215,7 @@
     <t xml:space="preserve">CP-ELY20008</t>
   </si>
   <si>
-    <t xml:space="preserve">GORRO CONO ELY GLOBO 6UN</t>
+    <t xml:space="preserve">Gorro Cono Ely Globo 6un</t>
   </si>
   <si>
     <t xml:space="preserve">0-0</t>
@@ -230,7 +230,7 @@
     <t xml:space="preserve">CP-ELY20046</t>
   </si>
   <si>
-    <t xml:space="preserve">CORNETA ELY GLOBOS 6UN</t>
+    <t xml:space="preserve">Corneta Ely Globos 6un</t>
   </si>
   <si>
     <t xml:space="preserve">CORNETA GLOBO</t>
@@ -239,7 +239,7 @@
     <t xml:space="preserve">XX-90002ROS</t>
   </si>
   <si>
-    <t xml:space="preserve">GLOBO Nº9 MONOCOLOR ROSADO 6UN</t>
+    <t xml:space="preserve">Globo Nº9 Monocolor Rosado 6un</t>
   </si>
   <si>
     <t xml:space="preserve">ORIGEN/MICRO J</t>
@@ -254,7 +254,7 @@
     <t xml:space="preserve">ELY-20007</t>
   </si>
   <si>
-    <t xml:space="preserve">GLOBO SURTIDO MEDIANO 6 UN</t>
+    <t xml:space="preserve">Globo Surtido Mediano 6 Un</t>
   </si>
   <si>
     <t xml:space="preserve">GLOBO N9 VERDE, ROSADO, AMARILLO,BLANCO, AZUL, ROJO)</t>
@@ -266,7 +266,7 @@
     <t xml:space="preserve">17898509283334</t>
   </si>
   <si>
-    <t xml:space="preserve">GLOBO N°9 SURTIDO 50 UN</t>
+    <t xml:space="preserve">Globo N°9 Surtido 50 Un</t>
   </si>
   <si>
     <t xml:space="preserve">ORIGEN/0-0</t>
@@ -278,7 +278,7 @@
     <t xml:space="preserve">NB-024 CAJA</t>
   </si>
   <si>
-    <t xml:space="preserve">GLOBO Nº9 MONOCOLOR AMARILLO 50UN</t>
+    <t xml:space="preserve">Globo Nº9 Monocolor Amarillo 50un</t>
   </si>
   <si>
     <t xml:space="preserve">GLOBO N9 AMARILLO</t>
@@ -287,13 +287,13 @@
     <t xml:space="preserve">NB-025 CAJA</t>
   </si>
   <si>
-    <t xml:space="preserve">GLOBO Nº9 MONOCOLOR ROJO 50UN</t>
+    <t xml:space="preserve">Globo Nº9 Monocolor Rojo 50un</t>
   </si>
   <si>
     <t xml:space="preserve">NB-026 CAJA</t>
   </si>
   <si>
-    <t xml:space="preserve">GLOBO Nº9 MONOCOLOR AZUL 50UN</t>
+    <t xml:space="preserve">Globo Nº9 Monocolor Azul 50un</t>
   </si>
   <si>
     <t xml:space="preserve">GLOBO N9 AZUL</t>
@@ -302,7 +302,7 @@
     <t xml:space="preserve">NB-027 CAJA</t>
   </si>
   <si>
-    <t xml:space="preserve">GLOBO Nº9 MONOCOLOR VERDE 50UN</t>
+    <t xml:space="preserve">Globo Nº9 Monocolor Verde 50un</t>
   </si>
   <si>
     <t xml:space="preserve">GLOBO N9 VERDE</t>
@@ -311,7 +311,7 @@
     <t xml:space="preserve">NB-028 CAJA</t>
   </si>
   <si>
-    <t xml:space="preserve">GLOBO Nº9 MONOCOLOR NARANJA 50UN</t>
+    <t xml:space="preserve">Globo Nº9 Monocolor Naranja 50un</t>
   </si>
   <si>
     <t xml:space="preserve">GLOBO N9 NARANJA</t>
@@ -320,13 +320,13 @@
     <t xml:space="preserve">NB-029 CAJA</t>
   </si>
   <si>
-    <t xml:space="preserve">GLOBO Nº9 MONOCOLOR ROSADO 50UN</t>
+    <t xml:space="preserve">Globo Nº9 Monocolor Rosado 50un</t>
   </si>
   <si>
     <t xml:space="preserve">NB-030 CAJA</t>
   </si>
   <si>
-    <t xml:space="preserve">GLOBO Nº9 MONOCOLOR BLANCO 50UN</t>
+    <t xml:space="preserve">Globo Nº9 Monocolor Blanco 50un</t>
   </si>
   <si>
     <t xml:space="preserve">GLOBO N9 BLANCO</t>
@@ -335,13 +335,13 @@
     <t xml:space="preserve">XX-90002AM</t>
   </si>
   <si>
-    <t xml:space="preserve">GLOBO Nº9 MONOCOLOR AMARILLO 6UN</t>
+    <t xml:space="preserve">Globo Nº9 Monocolor Amarillo 6un</t>
   </si>
   <si>
     <t xml:space="preserve">XX-90002RJ</t>
   </si>
   <si>
-    <t xml:space="preserve">GLOBO Nº9 MONOCOLOR ROJO 6UN</t>
+    <t xml:space="preserve">Globo Nº9 Monocolor Rojo 6un</t>
   </si>
   <si>
     <t xml:space="preserve">GLOBO N9 ROJO</t>
@@ -350,31 +350,31 @@
     <t xml:space="preserve">XX-90002AZ</t>
   </si>
   <si>
-    <t xml:space="preserve">GLOBO Nº9 MONOCOLOR AZUL 6UN</t>
+    <t xml:space="preserve">Globo Nº9 Monocolor Azul 6un</t>
   </si>
   <si>
     <t xml:space="preserve">XX-90002VE</t>
   </si>
   <si>
-    <t xml:space="preserve">GLOBO Nº9 MONOCOLOR VERDE 6UN</t>
+    <t xml:space="preserve">Globo Nº9 Monocolor Verde 6un</t>
   </si>
   <si>
     <t xml:space="preserve">XX-90002BL</t>
   </si>
   <si>
-    <t xml:space="preserve">GLOBO Nº9 MONOCOLOR BLANCO 6UN</t>
+    <t xml:space="preserve">Globo Nº9 Monocolor Blanco 6un</t>
   </si>
   <si>
     <t xml:space="preserve">XX-90002NJ</t>
   </si>
   <si>
-    <t xml:space="preserve">GLOBO Nº9 MONOCOLOR NARANJO 6UN</t>
+    <t xml:space="preserve">Globo Nº9 Monocolor Naranjo 6un</t>
   </si>
   <si>
     <t xml:space="preserve">ELY-20016*12</t>
   </si>
   <si>
-    <t xml:space="preserve">SERVILLETA DICU IMPRESA GLOBOS</t>
+    <t xml:space="preserve">Servilleta Dicu Impresa Globos</t>
   </si>
   <si>
     <t xml:space="preserve">SERVILLETA GLOBOS</t>
@@ -386,7 +386,7 @@
     <t xml:space="preserve">17805475004184</t>
   </si>
   <si>
-    <t xml:space="preserve">SERVILLETA INFANTIL ELY 20UN</t>
+    <t xml:space="preserve">Servilleta Infantil Ely 20un</t>
   </si>
   <si>
     <t xml:space="preserve">CERO</t>
@@ -401,7 +401,7 @@
     <t xml:space="preserve">ELY-20010</t>
   </si>
   <si>
-    <t xml:space="preserve">MANTEL ELY CUMPLEAÑOS DISPLAY BCO</t>
+    <t xml:space="preserve">Mantel Ely Cumpleaños Display Bco</t>
   </si>
   <si>
     <t xml:space="preserve">MANTEL BLANCO PEBD</t>
@@ -413,7 +413,7 @@
     <t xml:space="preserve">ELY-20009</t>
   </si>
   <si>
-    <t xml:space="preserve">MANTEL ELY IMPRESO GLOBOS</t>
+    <t xml:space="preserve">Mantel Ely Impreso Globos</t>
   </si>
   <si>
     <t xml:space="preserve">MICRO J </t>
@@ -428,7 +428,7 @@
     <t xml:space="preserve">17805475004191</t>
   </si>
   <si>
-    <t xml:space="preserve">MANTEL INFANTIL ELY</t>
+    <t xml:space="preserve">Mantel Infantil Ely</t>
   </si>
   <si>
     <t xml:space="preserve">MAN00612</t>
@@ -437,7 +437,7 @@
     <t xml:space="preserve">17805475006126</t>
   </si>
   <si>
-    <t xml:space="preserve">MANTEL BIOELY 1 UN</t>
+    <t xml:space="preserve">Mantel Bioely 1 Un</t>
   </si>
   <si>
     <t xml:space="preserve">MICRO D</t>
@@ -449,7 +449,7 @@
     <t xml:space="preserve">CP-ELY20011</t>
   </si>
   <si>
-    <t xml:space="preserve">PLATO ELY IMPRESO GLOBO 6UN</t>
+    <t xml:space="preserve">Plato Ely Impreso Globo 6un</t>
   </si>
   <si>
     <t xml:space="preserve">PLATO GLOBO </t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">17805475004160</t>
   </si>
   <si>
-    <t xml:space="preserve">PLATO INFANTIL ELY 10UN</t>
+    <t xml:space="preserve">Plato Infantil Ely 10un</t>
   </si>
   <si>
     <t xml:space="preserve">ZE-82067</t>
   </si>
   <si>
-    <t xml:space="preserve">PLATO 17CM TERMOFORMADO DROP IT! 6UN</t>
+    <t xml:space="preserve">Plato 17cm Termoformado Drop It! 6un</t>
   </si>
   <si>
     <t xml:space="preserve">DROP IT</t>
@@ -482,7 +482,7 @@
     <t xml:space="preserve">CT-01006008</t>
   </si>
   <si>
-    <t xml:space="preserve">PLATO 22CM TERMOFORMADO DROP IT! 6UN</t>
+    <t xml:space="preserve">Plato 22cm Termoformado Drop It! 6un</t>
   </si>
   <si>
     <t xml:space="preserve">PLATO PLASTICO 22CM DOMINGO/DROP IT/ELY PREMIUM</t>
@@ -497,13 +497,13 @@
     <t xml:space="preserve">97896211813203</t>
   </si>
   <si>
-    <t xml:space="preserve">PLATO 17CM TERMOFORMADO DROP IT! 20UN</t>
+    <t xml:space="preserve">Plato 17cm Termoformado Drop It! 20un</t>
   </si>
   <si>
     <t xml:space="preserve">CT-01006018</t>
   </si>
   <si>
-    <t xml:space="preserve">PLATO 22CM TERMOFORMADO DROP IT! 20UN</t>
+    <t xml:space="preserve">Plato 22cm Termoformado Drop It! 20un</t>
   </si>
   <si>
     <t xml:space="preserve">CT-01006029</t>
@@ -512,7 +512,7 @@
     <t xml:space="preserve">17898335076971</t>
   </si>
   <si>
-    <t xml:space="preserve">PLATO DROP IT! 17CM 6UN</t>
+    <t xml:space="preserve">Plato Drop It! 17cm 6un</t>
   </si>
   <si>
     <t xml:space="preserve">PLBIO-001</t>
@@ -521,7 +521,7 @@
     <t xml:space="preserve">17805475004139</t>
   </si>
   <si>
-    <t xml:space="preserve">PLATO BIOELY 17CM 10UN</t>
+    <t xml:space="preserve">Plato Bioely 17cm 10un</t>
   </si>
   <si>
     <t xml:space="preserve">N BIOELY</t>
@@ -536,7 +536,7 @@
     <t xml:space="preserve">17805475004146</t>
   </si>
   <si>
-    <t xml:space="preserve">PLATO 25CM BIOELY 10UN</t>
+    <t xml:space="preserve">Plato 25cm Bioely 10un</t>
   </si>
   <si>
     <t xml:space="preserve">G BIOELY</t>
@@ -551,7 +551,7 @@
     <t xml:space="preserve">17805475003903</t>
   </si>
   <si>
-    <t xml:space="preserve">BOWL BIOELY 270CC 10UN</t>
+    <t xml:space="preserve">Bowl Bioely 270cc 10un</t>
   </si>
   <si>
     <t xml:space="preserve">BOWL BIOELY 50X6</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">17805475005846</t>
   </si>
   <si>
-    <t xml:space="preserve">PLATO 17CM VERDE BIOELY 10 UN</t>
+    <t xml:space="preserve">Plato 17cm Verde Bioely 10 Un</t>
   </si>
   <si>
     <t xml:space="preserve">PLBIO-008</t>
@@ -575,7 +575,7 @@
     <t xml:space="preserve">17805475005853</t>
   </si>
   <si>
-    <t xml:space="preserve">PLATO 25CM VERDE BIOELY 10 UN</t>
+    <t xml:space="preserve">Plato 25cm Verde Bioely 10 Un</t>
   </si>
   <si>
     <t xml:space="preserve">BWBIO-004</t>
@@ -584,7 +584,7 @@
     <t xml:space="preserve">17805475005860</t>
   </si>
   <si>
-    <t xml:space="preserve">BOWL 270CC BIOELY VERDE 10 UN</t>
+    <t xml:space="preserve">Bowl 270cc Bioely Verde 10 Un</t>
   </si>
   <si>
     <t xml:space="preserve">PLBIO-005</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">17805475005761</t>
   </si>
   <si>
-    <t xml:space="preserve">PLATO 17CM ROSADO BIOELY 10 UN</t>
+    <t xml:space="preserve">Plato 17cm Rosado Bioely 10 Un</t>
   </si>
   <si>
     <t xml:space="preserve">PLBIO-006</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">17805475005778</t>
   </si>
   <si>
-    <t xml:space="preserve">PLATO 25CM ROSADO BIOELY 10 UN</t>
+    <t xml:space="preserve">Plato 25cm Rosado Bioely 10 Un</t>
   </si>
   <si>
     <t xml:space="preserve">BWBIO-003</t>
@@ -611,13 +611,13 @@
     <t xml:space="preserve">17805475005785</t>
   </si>
   <si>
-    <t xml:space="preserve">BOWL 270CC BIOELY ROSADO 10 UN</t>
+    <t xml:space="preserve">Bowl 270cc Bioely Rosado 10 Un</t>
   </si>
   <si>
     <t xml:space="preserve">DRBIO-00633</t>
   </si>
   <si>
-    <t xml:space="preserve">PLATO CAÑA AZU 17CM 6UN BIO DROP IT</t>
+    <t xml:space="preserve">Plato Caña Azu 17cm 6un Bio Drop It</t>
   </si>
   <si>
     <t xml:space="preserve">BIO DROP IT</t>
@@ -635,7 +635,7 @@
     <t xml:space="preserve">17805475006348</t>
   </si>
   <si>
-    <t xml:space="preserve">PLATO CAÑA AZU 22CM 6UN BIO DROP IT</t>
+    <t xml:space="preserve">Plato Caña Azu 22cm 6un Bio Drop It</t>
   </si>
   <si>
     <t xml:space="preserve">PLATP 23 CM CAÑA AZUCAR TUGOU</t>
@@ -644,19 +644,19 @@
     <t xml:space="preserve">DRBIO-00635</t>
   </si>
   <si>
-    <t xml:space="preserve">PLATO CAÑA AZU 17CM 20UN BIO DROP IT</t>
+    <t xml:space="preserve">Plato Caña Azu 17cm 20un Bio Drop It</t>
   </si>
   <si>
     <t xml:space="preserve">DRBIO-00636</t>
   </si>
   <si>
-    <t xml:space="preserve">PLATO CAÑA AZU 22CM 20UN BIO DROP IT</t>
+    <t xml:space="preserve">Plato Caña Azu 22cm 20un Bio Drop It</t>
   </si>
   <si>
     <t xml:space="preserve">DRBIO-00647</t>
   </si>
   <si>
-    <t xml:space="preserve">BOWL CAÑA AZUCAR 500 ML 3 UN BIO DROP IT</t>
+    <t xml:space="preserve">Bowl Caña Azucar 500 Ml 3 Un Bio Drop It</t>
   </si>
   <si>
     <t xml:space="preserve">ORIGEN/1</t>
@@ -671,7 +671,7 @@
     <t xml:space="preserve">ELY-20021</t>
   </si>
   <si>
-    <t xml:space="preserve">SORPRESA N° 4 CUMPLEAÑOS ELY</t>
+    <t xml:space="preserve">Sorpresa N° 4 Cumpleaños Ely</t>
   </si>
   <si>
     <t xml:space="preserve">MAQUILA EXTERNA</t>
@@ -680,7 +680,7 @@
     <t xml:space="preserve">ELY-20022</t>
   </si>
   <si>
-    <t xml:space="preserve">SORPRESA N° 5 CUMPLEAÑOS ELY</t>
+    <t xml:space="preserve">Sorpresa N° 5 Cumpleaños Ely</t>
   </si>
   <si>
     <t xml:space="preserve">ELY-20024</t>
@@ -689,7 +689,7 @@
     <t xml:space="preserve">17805475002555</t>
   </si>
   <si>
-    <t xml:space="preserve">SORPRESA SURTIDO 20UN</t>
+    <t xml:space="preserve">Sorpresa Surtido 20un</t>
   </si>
   <si>
     <t xml:space="preserve">18X20 </t>
@@ -698,7 +698,7 @@
     <t xml:space="preserve">ELY-20026</t>
   </si>
   <si>
-    <t xml:space="preserve">VASO DESECHABLE ELY GLOBOS 200CC 6UN</t>
+    <t xml:space="preserve">Vaso Desechable Ely Globos 200cc 6un</t>
   </si>
   <si>
     <t xml:space="preserve">CT-ELY-INFAN02</t>
@@ -707,13 +707,13 @@
     <t xml:space="preserve">17805475004177</t>
   </si>
   <si>
-    <t xml:space="preserve">VASO INFANTIL ELY 10UN</t>
+    <t xml:space="preserve">Vaso Infantil Ely 10un</t>
   </si>
   <si>
     <t xml:space="preserve">CT-01006022</t>
   </si>
   <si>
-    <t xml:space="preserve">VASO BLANCO 180CC 6UN DROP IT!</t>
+    <t xml:space="preserve">Vaso Blanco 180cc 6un Drop It!</t>
   </si>
   <si>
     <t xml:space="preserve">G DROP IT/ORIGEN</t>
@@ -728,7 +728,7 @@
     <t xml:space="preserve">CT-01006023</t>
   </si>
   <si>
-    <t xml:space="preserve">VASO TRANSP. 180CC 6UN DROP IT!</t>
+    <t xml:space="preserve">Vaso Transp. 180cc 6un Drop It!</t>
   </si>
   <si>
     <t xml:space="preserve">VASO TRANSP 7OZ CHEERS/BOOP</t>
@@ -737,7 +737,7 @@
     <t xml:space="preserve">CT-01006024</t>
   </si>
   <si>
-    <t xml:space="preserve">VASO BLANCO 300CC 6UN DROP IT!</t>
+    <t xml:space="preserve">Vaso Blanco 300cc 6un Drop It!</t>
   </si>
   <si>
     <t xml:space="preserve">VASO BLANCO 10OZ BOOP</t>
@@ -749,7 +749,7 @@
     <t xml:space="preserve">CT-01006025</t>
   </si>
   <si>
-    <t xml:space="preserve">VASO TRANSP DROP IT! 300CC 6UN</t>
+    <t xml:space="preserve">Vaso Transp Drop It! 300cc 6un</t>
   </si>
   <si>
     <t xml:space="preserve">VASO TRANSP 10OZ BOOP</t>
@@ -758,7 +758,7 @@
     <t xml:space="preserve">CT-01006026</t>
   </si>
   <si>
-    <t xml:space="preserve">VASO TRANSP DROP IT! 500CC 6UN</t>
+    <t xml:space="preserve">Vaso Transp Drop It! 500cc 6un</t>
   </si>
   <si>
     <t xml:space="preserve">VASO TRANSP.16OZ BOOP</t>
@@ -770,7 +770,7 @@
     <t xml:space="preserve">DR82243</t>
   </si>
   <si>
-    <t xml:space="preserve">VASO TERMICO 240CC 6UN DROP IT!</t>
+    <t xml:space="preserve">Vaso Termico 240cc 6un Drop It!</t>
   </si>
   <si>
     <t xml:space="preserve">G DROP IT</t>
@@ -782,13 +782,13 @@
     <t xml:space="preserve">CT-01006005</t>
   </si>
   <si>
-    <t xml:space="preserve">VASO TRANSP 500CC 6UN DROP IT!</t>
+    <t xml:space="preserve">Vaso Transp 500cc 6un Drop It!</t>
   </si>
   <si>
     <t xml:space="preserve">CT-01006013</t>
   </si>
   <si>
-    <t xml:space="preserve">VASO TRANSP 180CC 20UN DROP IT!</t>
+    <t xml:space="preserve">Vaso Transp 180cc 20un Drop It!</t>
   </si>
   <si>
     <t xml:space="preserve">VASO TRANSP. 7OZ CHEERS/BOOP</t>
@@ -797,7 +797,7 @@
     <t xml:space="preserve">CT-01006015</t>
   </si>
   <si>
-    <t xml:space="preserve">VASO TRANSP 300CC 20UN DROP IT!</t>
+    <t xml:space="preserve">Vaso Transp 300cc 20un Drop It!</t>
   </si>
   <si>
     <t xml:space="preserve">VASO TRANSP. 10PZ BOOP/ DROP IT </t>
@@ -806,13 +806,13 @@
     <t xml:space="preserve">DR81312</t>
   </si>
   <si>
-    <t xml:space="preserve">VASO TERMICO 240CC 20UN DROP IT!</t>
+    <t xml:space="preserve">Vaso Termico 240cc 20un Drop It!</t>
   </si>
   <si>
     <t xml:space="preserve">EW-WPEA006/07</t>
   </si>
   <si>
-    <t xml:space="preserve">VASO BICOLOR 500 CC</t>
+    <t xml:space="preserve">Vaso Bicolor 500 Cc</t>
   </si>
   <si>
     <t xml:space="preserve">K 60</t>
@@ -827,7 +827,7 @@
     <t xml:space="preserve">17805475004061</t>
   </si>
   <si>
-    <t xml:space="preserve">VASO 350CC BIOELY 10UN</t>
+    <t xml:space="preserve">Vaso 350cc Bioely 10un</t>
   </si>
   <si>
     <t xml:space="preserve">N - G BIOELY </t>
@@ -842,7 +842,7 @@
     <t xml:space="preserve">17805475004078</t>
   </si>
   <si>
-    <t xml:space="preserve">VASO 500CC BIOELY 10UN</t>
+    <t xml:space="preserve">Vaso 500cc Bioely 10un</t>
   </si>
   <si>
     <t xml:space="preserve">VASO 500 BIOELY 50X10</t>
@@ -854,7 +854,7 @@
     <t xml:space="preserve">17805475006119</t>
   </si>
   <si>
-    <t xml:space="preserve">VASO 500CC ROJO BIOELY 10 UN</t>
+    <t xml:space="preserve">Vaso 500cc Rojo Bioely 10 Un</t>
   </si>
   <si>
     <t xml:space="preserve">G BIOELY/ORIGEN</t>
@@ -869,7 +869,7 @@
     <t xml:space="preserve">17805475005792</t>
   </si>
   <si>
-    <t xml:space="preserve">VASO 350CC VERDE BIOELY 10 UN</t>
+    <t xml:space="preserve">Vaso 350cc Verde Bioely 10 Un</t>
   </si>
   <si>
     <t xml:space="preserve">VSBIO-008</t>
@@ -878,7 +878,7 @@
     <t xml:space="preserve">17805475005808</t>
   </si>
   <si>
-    <t xml:space="preserve">VASO 500CC VERDE BIOELY 10 UN</t>
+    <t xml:space="preserve">Vaso 500cc Verde Bioely 10 Un</t>
   </si>
   <si>
     <t xml:space="preserve">VSBIO-005</t>
@@ -887,7 +887,7 @@
     <t xml:space="preserve">17805475005716</t>
   </si>
   <si>
-    <t xml:space="preserve">VASO 350CC ROSADO BIOELY 10 UN</t>
+    <t xml:space="preserve">Vaso 350cc Rosado Bioely 10 Un</t>
   </si>
   <si>
     <t xml:space="preserve">VSBIO-006</t>
@@ -896,7 +896,7 @@
     <t xml:space="preserve">17805475005723</t>
   </si>
   <si>
-    <t xml:space="preserve">VASO 500CC ROSADO BIOELY 10 UN</t>
+    <t xml:space="preserve">Vaso 500cc Rosado Bioely 10 Un</t>
   </si>
   <si>
     <t xml:space="preserve">VAS00677</t>
@@ -905,7 +905,7 @@
     <t xml:space="preserve">17805475006775</t>
   </si>
   <si>
-    <t xml:space="preserve">VASO CAFE PLA BIOELY 10OZ 20 UND</t>
+    <t xml:space="preserve">Vaso Cafe Pla Bioely 10oz 20 Und</t>
   </si>
   <si>
     <t xml:space="preserve">VASO 12OZ PLA DISEÑO VERDE (GREEN CUP/IMPORTADO)</t>
@@ -917,7 +917,7 @@
     <t xml:space="preserve">17805475006805</t>
   </si>
   <si>
-    <t xml:space="preserve">TAPA VASO CAFE PLA BIOELY 10-12OZ 20UND</t>
+    <t xml:space="preserve">Tapa Vaso Cafe Pla Bioely 10-12oz 20und</t>
   </si>
   <si>
     <t xml:space="preserve">20X36</t>
@@ -929,13 +929,13 @@
     <t xml:space="preserve">17805475007215</t>
   </si>
   <si>
-    <t xml:space="preserve">VASO CAFE PLA BIOELY 10OZ 10 UND</t>
+    <t xml:space="preserve">Vaso Cafe Pla Bioely 10oz 10 Und</t>
   </si>
   <si>
     <t xml:space="preserve">DRBIO-00638</t>
   </si>
   <si>
-    <t xml:space="preserve">VASO CAFE PLA 240CC 6UN BIO DROP IT</t>
+    <t xml:space="preserve">Vaso Cafe Pla 240cc 6un Bio Drop It</t>
   </si>
   <si>
     <t xml:space="preserve">ORIGEN/4 ANTIGUA</t>
@@ -953,7 +953,7 @@
     <t xml:space="preserve">17805475006539</t>
   </si>
   <si>
-    <t xml:space="preserve">VASO TRANSP 280CC 6 UN PLA BIO DROP IT</t>
+    <t xml:space="preserve">Vaso Transp 280cc 6 Un Pla Bio Drop It</t>
   </si>
   <si>
     <t xml:space="preserve">DRBIO-00656</t>
@@ -962,7 +962,7 @@
     <t xml:space="preserve">17805475006560</t>
   </si>
   <si>
-    <t xml:space="preserve">VASO TRANSP 500CC 6UN PLA BIO DROP IT</t>
+    <t xml:space="preserve">Vaso Transp 500cc 6un Pla Bio Drop It</t>
   </si>
   <si>
     <t xml:space="preserve">DRBIO-00654</t>
@@ -971,13 +971,13 @@
     <t xml:space="preserve">17805475006546</t>
   </si>
   <si>
-    <t xml:space="preserve">VASO TRANSP 280CC 20 UN PLA BIO DROP IT</t>
+    <t xml:space="preserve">Vaso Transp 280cc 20 Un Pla Bio Drop It</t>
   </si>
   <si>
     <t xml:space="preserve">DRBIO-00639</t>
   </si>
   <si>
-    <t xml:space="preserve">VASO CAFE 240CC 20 UN PLA BIO DROP IT</t>
+    <t xml:space="preserve">Vaso Cafe 240cc 20 Un Pla Bio Drop It</t>
   </si>
   <si>
     <t xml:space="preserve">ORIGEN/1/K60</t>
@@ -986,7 +986,7 @@
     <t xml:space="preserve">DRBIO-00640</t>
   </si>
   <si>
-    <t xml:space="preserve">VASO CAFE 180 CC 6 UN PLA BIO DROP IT</t>
+    <t xml:space="preserve">Vaso Cafe 180 Cc 6 Un Pla Bio Drop It</t>
   </si>
   <si>
     <t xml:space="preserve">VASO 6OZ BLANCO ECO MERKAT/ECO UNIMARC</t>
@@ -995,94 +995,94 @@
     <t xml:space="preserve">DRBIO-00641</t>
   </si>
   <si>
-    <t xml:space="preserve">VASO CAFE 180 CC 20 UN PLA BIO DROP IT</t>
+    <t xml:space="preserve">Vaso Cafe 180 Cc 20 Un Pla Bio Drop It</t>
   </si>
   <si>
     <t xml:space="preserve">JT-VLG0 CAJA</t>
   </si>
   <si>
-    <t xml:space="preserve">VELA CUMPLEAÑOS GLIT N°0</t>
+    <t xml:space="preserve">Vela Cumpleaños Glit N°0</t>
   </si>
   <si>
     <t xml:space="preserve">JT-VLG1 CAJA</t>
   </si>
   <si>
-    <t xml:space="preserve">VELA CUMPLEAÑOS GLIT N°1</t>
+    <t xml:space="preserve">Vela Cumpleaños Glit N°1</t>
   </si>
   <si>
     <t xml:space="preserve">JT-VLG2 CAJA</t>
   </si>
   <si>
-    <t xml:space="preserve">VELA CUMPLEAÑOS GLIT N°2</t>
+    <t xml:space="preserve">Vela Cumpleaños Glit N°2</t>
   </si>
   <si>
     <t xml:space="preserve">JT-VLG3 CAJA</t>
   </si>
   <si>
-    <t xml:space="preserve">VELA CUMPLEAÑOS GLIT N°3</t>
+    <t xml:space="preserve">Vela Cumpleaños Glit N°3</t>
   </si>
   <si>
     <t xml:space="preserve">JT-VLG4 CAJA</t>
   </si>
   <si>
-    <t xml:space="preserve">VELA CUMPLEAÑOS GLIT N°4</t>
+    <t xml:space="preserve">Vela Cumpleaños Glit N°4</t>
   </si>
   <si>
     <t xml:space="preserve">JT-VLG5 CAJA</t>
   </si>
   <si>
-    <t xml:space="preserve">VELA CUMPLEAÑOS GLIT N°5</t>
+    <t xml:space="preserve">Vela Cumpleaños Glit N°5</t>
   </si>
   <si>
     <t xml:space="preserve">JT-VLG6 CAJA</t>
   </si>
   <si>
-    <t xml:space="preserve">VELA CUMPLEAÑOS GLIT N°6</t>
+    <t xml:space="preserve">Vela Cumpleaños Glit N°6</t>
   </si>
   <si>
     <t xml:space="preserve">JT-VLG7 CAJA</t>
   </si>
   <si>
-    <t xml:space="preserve">VELA CUMPLEAÑOS GLIT N°7</t>
+    <t xml:space="preserve">Vela Cumpleaños Glit N°7</t>
   </si>
   <si>
     <t xml:space="preserve">JT-VLG8 CAJA</t>
   </si>
   <si>
-    <t xml:space="preserve">VELA CUMPLEAÑOS GLIT N°8</t>
+    <t xml:space="preserve">Vela Cumpleaños Glit N°8</t>
   </si>
   <si>
     <t xml:space="preserve">JT-VLG9 CAJA</t>
   </si>
   <si>
-    <t xml:space="preserve">VELA CUMPLEAÑOS GLIT N°9</t>
+    <t xml:space="preserve">Vela Cumpleaños Glit N°9</t>
   </si>
   <si>
     <t xml:space="preserve">JT-VLG? CAJA</t>
   </si>
   <si>
-    <t xml:space="preserve">VELA CUMPLEAÑOS GLIT "?"</t>
+    <t xml:space="preserve">Vela Cumpleaños Glit "?"</t>
   </si>
   <si>
     <t xml:space="preserve">JT-HF1024BN CAJA</t>
   </si>
   <si>
-    <t xml:space="preserve">VELA ELY LARGAS 24UN</t>
+    <t xml:space="preserve">Vela Ely Largas 24un</t>
   </si>
   <si>
     <t xml:space="preserve">JT-HF1024BBLUE CAJA</t>
   </si>
   <si>
-    <t xml:space="preserve">VELA ELY CHICA AZUL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VELA ELY CHICA NEON</t>
+    <t xml:space="preserve">Vela Ely Chica Azul</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vela Ely Chica Neon</t>
   </si>
   <si>
     <t xml:space="preserve">JT-HF1024BRED CAJA</t>
   </si>
   <si>
-    <t xml:space="preserve">VELA ELY CHICA ROJO</t>
+    <t xml:space="preserve">Vela Ely Chica Rojo</t>
   </si>
   <si>
     <t xml:space="preserve">JT-PL12CAJA*24</t>
@@ -1091,7 +1091,7 @@
     <t xml:space="preserve">17896380170606</t>
   </si>
   <si>
-    <t xml:space="preserve">VELA LARGA 12 UN</t>
+    <t xml:space="preserve">Vela Larga 12 Un</t>
   </si>
   <si>
     <t xml:space="preserve">NC-07731</t>
@@ -1100,7 +1100,7 @@
     <t xml:space="preserve">17896359015006</t>
   </si>
   <si>
-    <t xml:space="preserve">SET CUBIERTOS DESECHABLES 3UN DROP IT!</t>
+    <t xml:space="preserve">Set Cubiertos Desechables 3un Drop It!</t>
   </si>
   <si>
     <t xml:space="preserve">0-0/ORIGEN</t>
@@ -1118,25 +1118,25 @@
     <t xml:space="preserve">97896211813104</t>
   </si>
   <si>
-    <t xml:space="preserve">CUCHARAS DESECHABLES 10UN DROP IT!</t>
+    <t xml:space="preserve">Cucharas Desechables 10un Drop It!</t>
   </si>
   <si>
     <t xml:space="preserve">NC-83060</t>
   </si>
   <si>
-    <t xml:space="preserve">TENEDORES DESECHABLE 10UN DROP IT!</t>
+    <t xml:space="preserve">Tenedores Desechable 10un Drop It!</t>
   </si>
   <si>
     <t xml:space="preserve">NC-81319</t>
   </si>
   <si>
-    <t xml:space="preserve">CUCHILLOS H TIBURON DESECH 10UN DROP IT!</t>
+    <t xml:space="preserve">Cuchillos H Tiburon Desech 10un Drop It!</t>
   </si>
   <si>
     <t xml:space="preserve">NC-90483</t>
   </si>
   <si>
-    <t xml:space="preserve">CUCHARITAS CAFE DROP ITT 10 UN</t>
+    <t xml:space="preserve">Cucharitas Cafe Drop Itt 10 Un</t>
   </si>
   <si>
     <t xml:space="preserve">CT-HG-XYFD-02</t>
@@ -1145,7 +1145,7 @@
     <t xml:space="preserve">17805475004108</t>
   </si>
   <si>
-    <t xml:space="preserve">CUCHILLO BIOELY 10UN</t>
+    <t xml:space="preserve">Cuchillo Bioely 10un</t>
   </si>
   <si>
     <t xml:space="preserve">CUCHILLO BIOELY</t>
@@ -1157,7 +1157,7 @@
     <t xml:space="preserve">17805475004115</t>
   </si>
   <si>
-    <t xml:space="preserve">TENEDOR BIOELY 10UN</t>
+    <t xml:space="preserve">Tenedor Bioely 10un</t>
   </si>
   <si>
     <t xml:space="preserve">TENEDOR BIOELY</t>
@@ -1169,7 +1169,7 @@
     <t xml:space="preserve">17805475004122</t>
   </si>
   <si>
-    <t xml:space="preserve">CUCHARA BIOELY 10UN</t>
+    <t xml:space="preserve">Cuchara Bioely 10un</t>
   </si>
   <si>
     <t xml:space="preserve">CUCHARA BIOELY</t>
@@ -1181,7 +1181,7 @@
     <t xml:space="preserve">17805475006256</t>
   </si>
   <si>
-    <t xml:space="preserve">CUCHILLO BIOELY VERDE 10 UN</t>
+    <t xml:space="preserve">Cuchillo Bioely Verde 10 Un</t>
   </si>
   <si>
     <t xml:space="preserve">CUCHILLO VERDE BIOELY</t>
@@ -1193,7 +1193,7 @@
     <t xml:space="preserve">17805475006294</t>
   </si>
   <si>
-    <t xml:space="preserve">TENEDOR BIOELY VERDE 10 UN</t>
+    <t xml:space="preserve">Tenedor Bioely Verde 10 Un</t>
   </si>
   <si>
     <t xml:space="preserve">TENEDOR VERDE BIOELY</t>
@@ -1205,7 +1205,7 @@
     <t xml:space="preserve">17805475006270</t>
   </si>
   <si>
-    <t xml:space="preserve">CUCHARA BIOELY VERDE 10 UN</t>
+    <t xml:space="preserve">Cuchara Bioely Verde 10 Un</t>
   </si>
   <si>
     <t xml:space="preserve">CUCHARA VERDE BIOELY</t>
@@ -1217,7 +1217,7 @@
     <t xml:space="preserve">17805475006263</t>
   </si>
   <si>
-    <t xml:space="preserve">CUCHILLO BIOELY ROSADO 10 UN</t>
+    <t xml:space="preserve">Cuchillo Bioely Rosado 10 Un</t>
   </si>
   <si>
     <t xml:space="preserve">CUCHILLO ROSADO BIOELY</t>
@@ -1229,7 +1229,7 @@
     <t xml:space="preserve">17805475006317</t>
   </si>
   <si>
-    <t xml:space="preserve">TENEDOR BIOELY ROSADO 10 UN</t>
+    <t xml:space="preserve">Tenedor Bioely Rosado 10 Un</t>
   </si>
   <si>
     <t xml:space="preserve">TENEDOR ROSADO BIOELY</t>
@@ -1241,7 +1241,7 @@
     <t xml:space="preserve">17805475006287</t>
   </si>
   <si>
-    <t xml:space="preserve">CUCHARA BIOELY ROSADO 10 UN</t>
+    <t xml:space="preserve">Cuchara Bioely Rosado 10 Un</t>
   </si>
   <si>
     <t xml:space="preserve">CUCHARA ROSADA BIOELY</t>
@@ -1250,7 +1250,7 @@
     <t xml:space="preserve">DRBIO-00642</t>
   </si>
   <si>
-    <t xml:space="preserve">SET CUBIERTOS 9UN PLA BIO DROP IT</t>
+    <t xml:space="preserve">Set Cubiertos 9un Pla Bio Drop It</t>
   </si>
   <si>
     <t xml:space="preserve">CUBIERTOS BIOELY</t>
@@ -1262,7 +1262,7 @@
     <t xml:space="preserve">17805475006430</t>
   </si>
   <si>
-    <t xml:space="preserve">CUCHARAS 10UN PLA BIO DROP IT</t>
+    <t xml:space="preserve">Cucharas 10un Pla Bio Drop It</t>
   </si>
   <si>
     <t xml:space="preserve">DRBIO-00644</t>
@@ -1271,7 +1271,7 @@
     <t xml:space="preserve">17805475006447</t>
   </si>
   <si>
-    <t xml:space="preserve">TENEDORES 10UN PLA BIO DROP IT</t>
+    <t xml:space="preserve">Tenedores 10un Pla Bio Drop It</t>
   </si>
   <si>
     <t xml:space="preserve">TENEDORES BIOELY</t>
@@ -1283,7 +1283,7 @@
     <t xml:space="preserve">17805475006454</t>
   </si>
   <si>
-    <t xml:space="preserve">CUCHILLOS 10UN PLA BIO DROP IT</t>
+    <t xml:space="preserve">Cuchillos 10un Pla Bio Drop It</t>
   </si>
   <si>
     <t xml:space="preserve">CUCHILLOS BIOELY</t>
@@ -1295,13 +1295,13 @@
     <t xml:space="preserve">17805475006461</t>
   </si>
   <si>
-    <t xml:space="preserve">CUCHARITAS CAFE 10 UN PLA BIO DROP IT</t>
+    <t xml:space="preserve">Cucharitas Cafe 10 Un Pla Bio Drop It</t>
   </si>
   <si>
     <t xml:space="preserve">DR28125X50D</t>
   </si>
   <si>
-    <t xml:space="preserve">BROCHETA 14,5CM</t>
+    <t xml:space="preserve">Brocheta 14,5cm</t>
   </si>
   <si>
     <t xml:space="preserve">BROCHETA DROP IT/BIOELY/LIDER</t>
@@ -1310,13 +1310,13 @@
     <t xml:space="preserve">DR28126X50D</t>
   </si>
   <si>
-    <t xml:space="preserve">BROCHETA 20 CM</t>
+    <t xml:space="preserve">Brocheta 20 Cm</t>
   </si>
   <si>
     <t xml:space="preserve">DR28127X50D</t>
   </si>
   <si>
-    <t xml:space="preserve">BROCHETA 25,5CM</t>
+    <t xml:space="preserve">Brocheta 25,5cm</t>
   </si>
   <si>
     <t xml:space="preserve">DR28343X50D</t>
@@ -1325,7 +1325,7 @@
     <t xml:space="preserve">17898509283341</t>
   </si>
   <si>
-    <t xml:space="preserve">BROCHETA 30CM </t>
+    <t xml:space="preserve">Brocheta 30cm </t>
   </si>
   <si>
     <t xml:space="preserve">BROCHETA DROP IT/UNIMARC/MERKAT</t>
@@ -1337,7 +1337,7 @@
     <t xml:space="preserve">17896380105332</t>
   </si>
   <si>
-    <t xml:space="preserve">MONDADIENTES</t>
+    <t xml:space="preserve">Mondadientes</t>
   </si>
   <si>
     <t xml:space="preserve">MONDADIENTES BIOELY/UNIMARC/MERKAT</t>
@@ -1346,7 +1346,7 @@
     <t xml:space="preserve">CT-09001016CAJA</t>
   </si>
   <si>
-    <t xml:space="preserve">FUENTE ALUM C/TAPA 2080ML (K60)</t>
+    <t xml:space="preserve">Fuente Alum C/Tapa 2080ml (K60)</t>
   </si>
   <si>
     <t xml:space="preserve">4X11</t>
@@ -1364,7 +1364,7 @@
     <t xml:space="preserve">CT-09001014CAJA</t>
   </si>
   <si>
-    <t xml:space="preserve">FUENTE ALUM C/TAPA 1500ML (K8)</t>
+    <t xml:space="preserve">Fuente Alum C/Tapa 1500ml (K8)</t>
   </si>
   <si>
     <t xml:space="preserve">4X10</t>
@@ -1382,7 +1382,7 @@
     <t xml:space="preserve">17805475006591</t>
   </si>
   <si>
-    <t xml:space="preserve"> PLATO 22CM CAÑA AZUCAR </t>
+    <t xml:space="preserve"> Plato 22cm Caña Azucar </t>
   </si>
   <si>
     <t xml:space="preserve">6X90</t>
@@ -1397,7 +1397,7 @@
     <t xml:space="preserve">17896001095035</t>
   </si>
   <si>
-    <t xml:space="preserve"> BANDEJA ALUMINIO PAVO 1162 (50)</t>
+    <t xml:space="preserve"> Bandeja Aluminio Pavo 1162 (50)</t>
   </si>
   <si>
     <t xml:space="preserve">X50</t>
@@ -1406,7 +1406,7 @@
     <t xml:space="preserve">ULTRAFOIL</t>
   </si>
   <si>
-    <t xml:space="preserve">PLATO 22CM 6 UNIDADES</t>
+    <t xml:space="preserve">Plato 22cm 6 Unidades</t>
   </si>
   <si>
     <t xml:space="preserve">6X40</t>
@@ -1415,7 +1415,7 @@
     <t xml:space="preserve">PLATO 22CM PLASTICO </t>
   </si>
   <si>
-    <t xml:space="preserve">VASO TERMICO 180CC 6 UNIDADES</t>
+    <t xml:space="preserve">Vaso Termico 180cc 6 Unidades</t>
   </si>
   <si>
     <t xml:space="preserve">6X45</t>
@@ -1430,7 +1430,7 @@
     <t xml:space="preserve">97896211830613</t>
   </si>
   <si>
-    <t xml:space="preserve"> VASO BLANCO 300CC PACK 28 X 20 UN DROP IT!</t>
+    <t xml:space="preserve"> Vaso Blanco 300cc Pack 28 X 20 Un Drop It!</t>
   </si>
   <si>
     <t xml:space="preserve">28X20</t>
@@ -2122,8 +2122,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O1048576"/>
-  <sheetFormatPr defaultColWidth="10.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:O137"/>
+  <sheetFormatPr defaultColWidth="10.75" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="15.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="16"/>
@@ -2139,7 +2139,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="3" width="9.13"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2186,7 +2186,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
         <v>15</v>
       </c>
@@ -2229,7 +2229,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
         <v>21</v>
       </c>
@@ -2274,7 +2274,7 @@
         <v>2650</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
         <v>25</v>
       </c>
@@ -2319,7 +2319,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="22.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
         <v>28</v>
       </c>
@@ -2364,7 +2364,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="22.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
         <v>34</v>
       </c>
@@ -2409,7 +2409,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
         <v>38</v>
       </c>
@@ -2456,7 +2456,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
         <v>43</v>
       </c>
@@ -2503,7 +2503,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
         <v>50</v>
       </c>
@@ -2550,7 +2550,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
         <v>54</v>
       </c>
@@ -2597,7 +2597,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
         <v>56</v>
       </c>
@@ -2644,7 +2644,7 @@
         <v>3800</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
         <v>59</v>
       </c>
@@ -2689,7 +2689,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
         <v>62</v>
       </c>
@@ -2734,7 +2734,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
         <v>67</v>
       </c>
@@ -2779,7 +2779,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
         <v>70</v>
       </c>
@@ -2824,7 +2824,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="26.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
         <v>75</v>
       </c>
@@ -2869,7 +2869,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="26.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
         <v>78</v>
       </c>
@@ -2916,7 +2916,7 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
         <v>83</v>
       </c>
@@ -2961,7 +2961,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
         <v>86</v>
       </c>
@@ -3006,7 +3006,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
         <v>88</v>
       </c>
@@ -3051,7 +3051,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
         <v>91</v>
       </c>
@@ -3096,7 +3096,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
         <v>94</v>
       </c>
@@ -3141,7 +3141,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
         <v>97</v>
       </c>
@@ -3186,7 +3186,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
         <v>99</v>
       </c>
@@ -3231,7 +3231,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
         <v>102</v>
       </c>
@@ -3276,7 +3276,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
         <v>104</v>
       </c>
@@ -3321,7 +3321,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
         <v>107</v>
       </c>
@@ -3366,7 +3366,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
         <v>109</v>
       </c>
@@ -3411,7 +3411,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
         <v>111</v>
       </c>
@@ -3456,7 +3456,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
         <v>113</v>
       </c>
@@ -3501,7 +3501,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
         <v>115</v>
       </c>
@@ -3546,7 +3546,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="22.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
         <v>118</v>
       </c>
@@ -3593,7 +3593,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
         <v>124</v>
       </c>
@@ -3638,7 +3638,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
         <v>128</v>
       </c>
@@ -3683,7 +3683,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
         <v>132</v>
       </c>
@@ -3730,7 +3730,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
         <v>135</v>
       </c>
@@ -3775,7 +3775,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
         <v>140</v>
       </c>
@@ -3820,7 +3820,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="s">
         <v>143</v>
       </c>
@@ -3867,7 +3867,7 @@
         <v>2350</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="33.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="26.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
         <v>146</v>
       </c>
@@ -3912,7 +3912,7 @@
         <v>6650</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="33.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="26.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="s">
         <v>151</v>
       </c>
@@ -3957,7 +3957,7 @@
         <v>6650</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="33.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="26.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
         <v>155</v>
       </c>
@@ -4002,7 +4002,7 @@
         <v>4600</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="33.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="26.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="s">
         <v>158</v>
       </c>
@@ -4047,7 +4047,7 @@
         <v>4600</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="33.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="26.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="s">
         <v>160</v>
       </c>
@@ -4092,7 +4092,7 @@
         <v>3800</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="s">
         <v>163</v>
       </c>
@@ -4139,7 +4139,7 @@
         <v>5050</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="22.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="s">
         <v>168</v>
       </c>
@@ -4186,7 +4186,7 @@
         <v>7700</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="4" t="s">
         <v>173</v>
       </c>
@@ -4233,7 +4233,7 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="s">
         <v>178</v>
       </c>
@@ -4280,7 +4280,7 @@
         <v>4750</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="4" t="s">
         <v>181</v>
       </c>
@@ -4327,7 +4327,7 @@
         <v>7900</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="4" t="s">
         <v>184</v>
       </c>
@@ -4374,7 +4374,7 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="4" t="s">
         <v>187</v>
       </c>
@@ -4421,7 +4421,7 @@
         <v>4650</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="4" t="s">
         <v>190</v>
       </c>
@@ -4468,7 +4468,7 @@
         <v>6950</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="4" t="s">
         <v>193</v>
       </c>
@@ -4515,7 +4515,7 @@
         <v>2600</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="22.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="4" t="s">
         <v>196</v>
       </c>
@@ -4560,7 +4560,7 @@
         <v>5900</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="22.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="4" t="s">
         <v>201</v>
       </c>
@@ -4607,7 +4607,7 @@
         <v>8950</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="22.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="4" t="s">
         <v>205</v>
       </c>
@@ -4652,7 +4652,7 @@
         <v>5200</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="22.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="4" t="s">
         <v>207</v>
       </c>
@@ -4697,7 +4697,7 @@
         <v>5900</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="22.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="4" t="s">
         <v>209</v>
       </c>
@@ -4744,7 +4744,7 @@
         <v>4250</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="4" t="s">
         <v>214</v>
       </c>
@@ -4789,7 +4789,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="4" t="s">
         <v>217</v>
       </c>
@@ -4834,7 +4834,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="4" t="s">
         <v>219</v>
       </c>
@@ -4881,7 +4881,7 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="4" t="s">
         <v>223</v>
       </c>
@@ -4926,7 +4926,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="4" t="s">
         <v>225</v>
       </c>
@@ -4973,7 +4973,7 @@
         <v>1550</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="22.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="4" t="s">
         <v>228</v>
       </c>
@@ -5018,7 +5018,7 @@
         <v>3050</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="22.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="4" t="s">
         <v>233</v>
       </c>
@@ -5063,7 +5063,7 @@
         <v>3150</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="22.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="4" t="s">
         <v>236</v>
       </c>
@@ -5108,7 +5108,7 @@
         <v>3350</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="22.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="4" t="s">
         <v>240</v>
       </c>
@@ -5153,7 +5153,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="22.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="4" t="s">
         <v>243</v>
       </c>
@@ -5198,7 +5198,7 @@
         <v>2350</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="4" t="s">
         <v>247</v>
       </c>
@@ -5243,7 +5243,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="22.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="4" t="s">
         <v>251</v>
       </c>
@@ -5288,7 +5288,7 @@
         <v>1850</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="22.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="4" t="s">
         <v>253</v>
       </c>
@@ -5333,7 +5333,7 @@
         <v>2550</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="22.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="4" t="s">
         <v>256</v>
       </c>
@@ -5378,7 +5378,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="4" t="s">
         <v>259</v>
       </c>
@@ -5423,7 +5423,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="4" t="s">
         <v>261</v>
       </c>
@@ -5468,7 +5468,7 @@
         <v>5600</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="4" t="s">
         <v>265</v>
       </c>
@@ -5515,7 +5515,7 @@
         <v>3800</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="4" t="s">
         <v>270</v>
       </c>
@@ -5562,7 +5562,7 @@
         <v>3100</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="22.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="4" t="s">
         <v>274</v>
       </c>
@@ -5609,7 +5609,7 @@
         <v>3750</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="4" t="s">
         <v>279</v>
       </c>
@@ -5656,7 +5656,7 @@
         <v>3550</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="4" t="s">
         <v>282</v>
       </c>
@@ -5703,7 +5703,7 @@
         <v>3050</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="4" t="s">
         <v>285</v>
       </c>
@@ -5750,7 +5750,7 @@
         <v>3700</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="4" t="s">
         <v>288</v>
       </c>
@@ -5797,7 +5797,7 @@
         <v>2950</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="33.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="26.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="4" t="s">
         <v>291</v>
       </c>
@@ -5844,7 +5844,7 @@
         <v>2600</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="4" t="s">
         <v>295</v>
       </c>
@@ -5887,7 +5887,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="33.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="26.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="4" t="s">
         <v>299</v>
       </c>
@@ -5934,7 +5934,7 @@
         <v>3050</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="33.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="4" t="s">
         <v>302</v>
       </c>
@@ -5981,7 +5981,7 @@
         <v>6450</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="4" t="s">
         <v>307</v>
       </c>
@@ -6028,7 +6028,7 @@
         <v>4700</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="4" t="s">
         <v>310</v>
       </c>
@@ -6075,7 +6075,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="4" t="s">
         <v>313</v>
       </c>
@@ -6122,7 +6122,7 @@
         <v>4450</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="33.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="4" t="s">
         <v>316</v>
       </c>
@@ -6169,7 +6169,7 @@
         <v>5300</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="22.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="4" t="s">
         <v>319</v>
       </c>
@@ -6216,7 +6216,7 @@
         <v>4600</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="22.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="4" t="s">
         <v>322</v>
       </c>
@@ -6263,7 +6263,7 @@
         <v>2950</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="4" t="s">
         <v>324</v>
       </c>
@@ -6308,7 +6308,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="4" t="s">
         <v>326</v>
       </c>
@@ -6353,7 +6353,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="4" t="s">
         <v>328</v>
       </c>
@@ -6398,7 +6398,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="4" t="s">
         <v>330</v>
       </c>
@@ -6443,7 +6443,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="4" t="s">
         <v>332</v>
       </c>
@@ -6488,7 +6488,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="4" t="s">
         <v>334</v>
       </c>
@@ -6533,7 +6533,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="4" t="s">
         <v>336</v>
       </c>
@@ -6578,7 +6578,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="4" t="s">
         <v>338</v>
       </c>
@@ -6623,7 +6623,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="4" t="s">
         <v>340</v>
       </c>
@@ -6668,7 +6668,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="4" t="s">
         <v>342</v>
       </c>
@@ -6713,7 +6713,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="4" t="s">
         <v>344</v>
       </c>
@@ -6758,7 +6758,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="4" t="s">
         <v>346</v>
       </c>
@@ -6803,7 +6803,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="4" t="s">
         <v>348</v>
       </c>
@@ -6848,7 +6848,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="4" t="s">
         <v>346</v>
       </c>
@@ -6893,7 +6893,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="4" t="s">
         <v>351</v>
       </c>
@@ -6938,7 +6938,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="4" t="s">
         <v>353</v>
       </c>
@@ -6985,7 +6985,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="107" customFormat="false" ht="33.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="4" t="s">
         <v>356</v>
       </c>
@@ -7032,7 +7032,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="33.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="4" t="s">
         <v>362</v>
       </c>
@@ -7079,7 +7079,7 @@
         <v>1650</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="33.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="4" t="s">
         <v>365</v>
       </c>
@@ -7124,7 +7124,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="33.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="4" t="s">
         <v>367</v>
       </c>
@@ -7169,7 +7169,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="111" customFormat="false" ht="33.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="4" t="s">
         <v>369</v>
       </c>
@@ -7214,7 +7214,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="4" t="s">
         <v>371</v>
       </c>
@@ -7261,7 +7261,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="4" t="s">
         <v>375</v>
       </c>
@@ -7308,7 +7308,7 @@
         <v>2550</v>
       </c>
     </row>
-    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="4" t="s">
         <v>379</v>
       </c>
@@ -7355,7 +7355,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="4" t="s">
         <v>383</v>
       </c>
@@ -7402,7 +7402,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="4" t="s">
         <v>387</v>
       </c>
@@ -7449,7 +7449,7 @@
         <v>2550</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="4" t="s">
         <v>391</v>
       </c>
@@ -7496,7 +7496,7 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="4" t="s">
         <v>395</v>
       </c>
@@ -7543,7 +7543,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="4" t="s">
         <v>399</v>
       </c>
@@ -7590,7 +7590,7 @@
         <v>2550</v>
       </c>
     </row>
-    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="4" t="s">
         <v>403</v>
       </c>
@@ -7637,7 +7637,7 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="4" t="s">
         <v>407</v>
       </c>
@@ -7682,7 +7682,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="4" t="s">
         <v>410</v>
       </c>
@@ -7729,7 +7729,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="4" t="s">
         <v>413</v>
       </c>
@@ -7776,7 +7776,7 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="4" t="s">
         <v>417</v>
       </c>
@@ -7823,7 +7823,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="4" t="s">
         <v>421</v>
       </c>
@@ -7870,7 +7870,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="126" customFormat="false" ht="22.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="4" t="s">
         <v>424</v>
       </c>
@@ -7917,7 +7917,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="127" customFormat="false" ht="22.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="4" t="s">
         <v>427</v>
       </c>
@@ -7964,7 +7964,7 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="128" customFormat="false" ht="22.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="4" t="s">
         <v>429</v>
       </c>
@@ -8011,7 +8011,7 @@
         <v>3800</v>
       </c>
     </row>
-    <row r="129" customFormat="false" ht="22.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="4" t="s">
         <v>431</v>
       </c>
@@ -8058,7 +8058,7 @@
         <v>4450</v>
       </c>
     </row>
-    <row r="130" customFormat="false" ht="22.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="4" t="s">
         <v>435</v>
       </c>
@@ -8105,7 +8105,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="4" t="s">
         <v>439</v>
       </c>
@@ -8150,7 +8150,7 @@
         <v>2350</v>
       </c>
     </row>
-    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="4" t="s">
         <v>445</v>
       </c>
@@ -8195,7 +8195,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="133" customFormat="false" ht="33.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" customFormat="false" ht="26.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="4" t="s">
         <v>449</v>
       </c>
@@ -8240,7 +8240,7 @@
         <v>8950</v>
       </c>
     </row>
-    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="4" t="s">
         <v>455</v>
       </c>
@@ -8287,7 +8287,7 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="4"/>
       <c r="B135" s="4"/>
       <c r="C135" s="5" t="n">
@@ -8326,7 +8326,7 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="4"/>
       <c r="B136" s="4" t="n">
         <v>1429589</v>
@@ -8369,7 +8369,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="137" customFormat="false" ht="33.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" customFormat="false" ht="26.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="4" t="s">
         <v>466</v>
       </c>
@@ -8416,10 +8416,6 @@
         <v>2250</v>
       </c>
     </row>
-    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <autoFilter ref="A1:O137"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -8439,7 +8435,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F46"/>
-  <sheetFormatPr defaultColWidth="10.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.75" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="38.86"/>
